--- a/results/tables/12_climate_CR2.xlsx
+++ b/results/tables/12_climate_CR2.xlsx
@@ -12,21 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
   <si>
-    <t xml:space="preserve">Coef</t>
-  </si>
-  <si>
     <t xml:space="preserve">beta</t>
   </si>
   <si>
     <t xml:space="preserve">SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null_value</t>
   </si>
   <si>
     <t xml:space="preserve">tstat</t>
@@ -392,89 +386,65 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.016260977024087</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0162609770240871</v>
+        <v>0.0106352518672644</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00915338040204837</v>
+        <v>-1.52896962169168</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2.34069772526282</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.77649964383084</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.00000016181195</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.326392912424283</v>
+        <v>0.248020620666538</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.000615480511241545</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000615480511241543</v>
+        <v>0.00029918525021568</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00130174155605613</v>
+        <v>2.05718868426118</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3.45639036514661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.472813138966122</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.00000025009344</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.718828877107548</v>
+        <v>0.119739949308659</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.0557415056584581</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0557415056584582</v>
+        <v>0.0103022478065863</v>
       </c>
       <c r="D4" t="n">
-        <v>0.148221508760113</v>
+        <v>-5.41061588742042</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2.67926978379649</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.37606893982352</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.00000024466675</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.771003085424371</v>
+        <v>0.0164770313990744</v>
       </c>
     </row>
   </sheetData>
